--- a/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
@@ -10,13 +10,14 @@
     <sheet name="Weekly Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Category Aggregation" sheetId="2" r:id="rId2"/>
     <sheet name="Product Quantity Detail" sheetId="3" r:id="rId3"/>
+    <sheet name="Sample Statistics" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>文件名称</t>
   </si>
@@ -42,10 +43,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>全部 笔订单-2026-02-26-10_51.csv</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
+    <t>0302.csv</t>
+  </si>
+  <si>
+    <t>0303.csv</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
   </si>
   <si>
     <t>日期</t>
@@ -69,7 +76,7 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>其他</t>
+    <t>头发护理精华</t>
   </si>
   <si>
     <t>电动鼻毛刀</t>
@@ -79,6 +86,12 @@
   </si>
   <si>
     <t>汇总</t>
+  </si>
+  <si>
+    <t>提示</t>
+  </si>
+  <si>
+    <t>无样品数据</t>
   </si>
 </sst>
 </file>
@@ -436,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -470,24 +483,50 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>22360</v>
+      </c>
+      <c r="D2">
+        <v>1118</v>
+      </c>
+      <c r="E2">
+        <v>15849</v>
+      </c>
+      <c r="F2">
+        <v>132.4</v>
+      </c>
+      <c r="G2">
+        <v>375</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>9373</v>
-      </c>
-      <c r="D2">
-        <v>468.65</v>
-      </c>
-      <c r="E2">
-        <v>6923</v>
-      </c>
-      <c r="F2">
-        <v>61.6</v>
-      </c>
-      <c r="G2">
-        <v>192.5</v>
-      </c>
-      <c r="H2">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>15406</v>
+      </c>
+      <c r="D3">
+        <v>770.3</v>
+      </c>
+      <c r="E3">
+        <v>10920</v>
+      </c>
+      <c r="F3">
+        <v>86.8</v>
+      </c>
+      <c r="G3">
+        <v>250</v>
+      </c>
+      <c r="H3">
         <v>0</v>
       </c>
     </row>
@@ -498,56 +537,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>11648</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>582.4</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8016</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -555,28 +594,80 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3">
-        <v>9373</v>
+        <v>10712</v>
       </c>
       <c r="D3">
-        <v>6923</v>
+        <v>535.6</v>
       </c>
       <c r="E3">
-        <v>61.60000000000001</v>
+        <v>7833</v>
       </c>
       <c r="F3">
-        <v>192.5</v>
+        <v>62.4</v>
       </c>
       <c r="G3">
+        <v>200</v>
+      </c>
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="H3">
-        <v>468.65</v>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>7372</v>
+      </c>
+      <c r="D4">
+        <v>368.6</v>
+      </c>
+      <c r="E4">
+        <v>5184</v>
+      </c>
+      <c r="F4">
+        <v>40</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>8034</v>
+      </c>
+      <c r="D5">
+        <v>401.7</v>
+      </c>
+      <c r="E5">
+        <v>5736</v>
+      </c>
+      <c r="F5">
+        <v>46.8</v>
+      </c>
+      <c r="G5">
+        <v>150</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -586,31 +677,74 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>文件名称</t>
   </si>
@@ -49,12 +49,18 @@
     <t>0303.csv</t>
   </si>
   <si>
+    <t>0304.csv</t>
+  </si>
+  <si>
     <t>2026-03-02</t>
   </si>
   <si>
     <t>2026-03-03</t>
   </si>
   <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -76,13 +82,19 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>电动鼻毛刀</t>
+  </si>
+  <si>
     <t>头发护理精华</t>
   </si>
   <si>
-    <t>电动鼻毛刀</t>
-  </si>
-  <si>
     <t>商品名称</t>
+  </si>
+  <si>
+    <t>剪影贴纸</t>
   </si>
   <si>
     <t>汇总</t>
@@ -449,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -483,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>22360</v>
@@ -495,10 +507,10 @@
         <v>15849</v>
       </c>
       <c r="F2">
-        <v>132.4</v>
+        <v>62.4</v>
       </c>
       <c r="G2">
-        <v>375</v>
+        <v>200</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -509,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>15406</v>
@@ -521,12 +533,38 @@
         <v>10920</v>
       </c>
       <c r="F3">
-        <v>86.8</v>
+        <v>56.8</v>
       </c>
       <c r="G3">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>24402</v>
+      </c>
+      <c r="D4">
+        <v>1220.1</v>
+      </c>
+      <c r="E4">
+        <v>17572</v>
+      </c>
+      <c r="F4">
+        <v>117</v>
+      </c>
+      <c r="G4">
+        <v>375</v>
+      </c>
+      <c r="H4">
         <v>0</v>
       </c>
     </row>
@@ -537,41 +575,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>11648</v>
@@ -583,10 +621,10 @@
         <v>8016</v>
       </c>
       <c r="F2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -594,10 +632,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>10712</v>
@@ -620,25 +658,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>7372</v>
+        <v>4992</v>
       </c>
       <c r="D4">
-        <v>368.6</v>
+        <v>249.6</v>
       </c>
       <c r="E4">
-        <v>5184</v>
+        <v>3154</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -646,27 +684,105 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5">
+        <v>2380</v>
+      </c>
+      <c r="D5">
+        <v>119</v>
+      </c>
+      <c r="E5">
+        <v>2030</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>25</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
         <v>8034</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>401.7</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>5736</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>46.8</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>150</v>
       </c>
-      <c r="H5">
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>3328</v>
+      </c>
+      <c r="D7">
+        <v>166.4</v>
+      </c>
+      <c r="E7">
+        <v>2628</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>21074</v>
+      </c>
+      <c r="D8">
+        <v>1053.7</v>
+      </c>
+      <c r="E8">
+        <v>14944</v>
+      </c>
+      <c r="F8">
+        <v>117</v>
+      </c>
+      <c r="G8">
+        <v>375</v>
+      </c>
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
@@ -677,23 +793,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>8</v>
@@ -701,27 +820,50 @@
       <c r="C2">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5">
         <v>15</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>10</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -736,7 +878,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -744,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,22 +43,28 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0302.csv</t>
-  </si>
-  <si>
-    <t>0303.csv</t>
-  </si>
-  <si>
-    <t>0304.csv</t>
-  </si>
-  <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
-    <t>2026-03-03</t>
-  </si>
-  <si>
-    <t>2026-03-04</t>
+    <t>0308.csv</t>
+  </si>
+  <si>
+    <t>0309.csv</t>
+  </si>
+  <si>
+    <t>0310.csv</t>
+  </si>
+  <si>
+    <t>0311.csv</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-11</t>
   </si>
   <si>
     <t>日期</t>
@@ -85,12 +91,12 @@
     <t>其他</t>
   </si>
   <si>
+    <t>头发护理精华</t>
+  </si>
+  <si>
     <t>电动鼻毛刀</t>
   </si>
   <si>
-    <t>头发护理精华</t>
-  </si>
-  <si>
     <t>商品名称</t>
   </si>
   <si>
@@ -100,10 +106,7 @@
     <t>汇总</t>
   </si>
   <si>
-    <t>提示</t>
-  </si>
-  <si>
-    <t>无样品数据</t>
+    <t>总样品数</t>
   </si>
 </sst>
 </file>
@@ -461,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -495,22 +498,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>22360</v>
+        <v>17205</v>
       </c>
       <c r="D2">
-        <v>1118</v>
+        <v>860.25</v>
       </c>
       <c r="E2">
-        <v>15849</v>
+        <v>13022</v>
       </c>
       <c r="F2">
-        <v>62.4</v>
+        <v>33.4</v>
       </c>
       <c r="G2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -521,25 +524,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>15406</v>
+        <v>16994</v>
       </c>
       <c r="D3">
-        <v>770.3</v>
+        <v>849.7</v>
       </c>
       <c r="E3">
-        <v>10920</v>
+        <v>11963</v>
       </c>
       <c r="F3">
-        <v>56.8</v>
+        <v>66.8</v>
       </c>
       <c r="G3">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -547,25 +550,51 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>24402</v>
+        <v>14006</v>
       </c>
       <c r="D4">
-        <v>1220.1</v>
+        <v>700.3</v>
       </c>
       <c r="E4">
-        <v>17572</v>
+        <v>9957</v>
       </c>
       <c r="F4">
-        <v>117</v>
+        <v>41.2</v>
       </c>
       <c r="G4">
-        <v>375</v>
+        <v>125</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>12205</v>
+      </c>
+      <c r="D5">
+        <v>610.25</v>
+      </c>
+      <c r="E5">
+        <v>7740</v>
+      </c>
+      <c r="F5">
+        <v>61.2</v>
+      </c>
+      <c r="G5">
+        <v>175</v>
+      </c>
+      <c r="H5">
+        <v>65.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -575,41 +604,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>11648</v>
@@ -618,7 +647,7 @@
         <v>582.4</v>
       </c>
       <c r="E2">
-        <v>8016</v>
+        <v>9041</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -632,25 +661,25 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>10712</v>
+        <v>1540</v>
       </c>
       <c r="D3">
-        <v>535.6</v>
+        <v>77</v>
       </c>
       <c r="E3">
-        <v>7833</v>
+        <v>1190</v>
       </c>
       <c r="F3">
-        <v>62.4</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -661,22 +690,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4">
-        <v>4992</v>
+        <v>4017</v>
       </c>
       <c r="D4">
-        <v>249.6</v>
+        <v>200.85</v>
       </c>
       <c r="E4">
-        <v>3154</v>
+        <v>2791</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -684,25 +713,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5">
-        <v>2380</v>
+        <v>3328</v>
       </c>
       <c r="D5">
-        <v>119</v>
+        <v>166.4</v>
       </c>
       <c r="E5">
-        <v>2030</v>
+        <v>2497</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -710,25 +739,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>8034</v>
+        <v>5632</v>
       </c>
       <c r="D6">
-        <v>401.7</v>
+        <v>281.6</v>
       </c>
       <c r="E6">
-        <v>5736</v>
+        <v>4274</v>
       </c>
       <c r="F6">
-        <v>46.8</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -739,51 +768,181 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>3328</v>
+        <v>8034</v>
       </c>
       <c r="D7">
-        <v>166.4</v>
+        <v>401.7</v>
       </c>
       <c r="E7">
-        <v>2628</v>
+        <v>5192</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>46.8</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>21074</v>
+        <v>6656</v>
       </c>
       <c r="D8">
-        <v>1053.7</v>
+        <v>332.8</v>
       </c>
       <c r="E8">
-        <v>14944</v>
+        <v>4456</v>
       </c>
       <c r="F8">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>1994</v>
+      </c>
+      <c r="D9">
+        <v>99.7</v>
+      </c>
+      <c r="E9">
+        <v>1644</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>25</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>5356</v>
+      </c>
+      <c r="D10">
+        <v>267.8</v>
+      </c>
+      <c r="E10">
+        <v>3857</v>
+      </c>
+      <c r="F10">
+        <v>31.2</v>
+      </c>
+      <c r="G10">
+        <v>100</v>
+      </c>
+      <c r="H10">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11">
+        <v>3328</v>
+      </c>
+      <c r="D11">
+        <v>166.4</v>
+      </c>
+      <c r="E11">
+        <v>2311</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>3521</v>
+      </c>
+      <c r="D12">
+        <v>176.05</v>
+      </c>
+      <c r="E12">
+        <v>2066</v>
+      </c>
+      <c r="F12">
+        <v>30</v>
+      </c>
+      <c r="G12">
+        <v>75</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>5356</v>
+      </c>
+      <c r="D13">
+        <v>267.8</v>
+      </c>
+      <c r="E13">
+        <v>3363</v>
+      </c>
+      <c r="F13">
+        <v>31.2</v>
+      </c>
+      <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13">
+        <v>65.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -793,77 +952,92 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>7</v>
       </c>
       <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -873,20 +1047,58 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,28 +43,10 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0308.csv</t>
-  </si>
-  <si>
-    <t>0309.csv</t>
-  </si>
-  <si>
-    <t>0310.csv</t>
-  </si>
-  <si>
-    <t>0311.csv</t>
-  </si>
-  <si>
-    <t>2026-03-08</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
-    <t>2026-03-11</t>
+    <t>直邮店-0315.csv</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>日期</t>
@@ -464,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -498,103 +480,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>17205</v>
+        <v>42793</v>
       </c>
       <c r="D2">
-        <v>860.25</v>
+        <v>2139.65</v>
       </c>
       <c r="E2">
-        <v>13022</v>
+        <v>29719</v>
       </c>
       <c r="F2">
-        <v>33.4</v>
+        <v>157</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>475</v>
       </c>
       <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>16994</v>
-      </c>
-      <c r="D3">
-        <v>849.7</v>
-      </c>
-      <c r="E3">
-        <v>11963</v>
-      </c>
-      <c r="F3">
-        <v>66.8</v>
-      </c>
-      <c r="G3">
-        <v>200</v>
-      </c>
-      <c r="H3">
-        <v>65.59999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>14006</v>
-      </c>
-      <c r="D4">
-        <v>700.3</v>
-      </c>
-      <c r="E4">
-        <v>9957</v>
-      </c>
-      <c r="F4">
-        <v>41.2</v>
-      </c>
-      <c r="G4">
-        <v>125</v>
-      </c>
-      <c r="H4">
-        <v>65.59999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>12205</v>
-      </c>
-      <c r="D5">
-        <v>610.25</v>
-      </c>
-      <c r="E5">
-        <v>7740</v>
-      </c>
-      <c r="F5">
-        <v>61.2</v>
-      </c>
-      <c r="G5">
-        <v>175</v>
-      </c>
-      <c r="H5">
-        <v>65.59999999999999</v>
+        <v>196.8</v>
       </c>
     </row>
   </sheetData>
@@ -604,50 +508,50 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C2">
-        <v>11648</v>
+        <v>13312</v>
       </c>
       <c r="D2">
-        <v>582.4</v>
+        <v>665.6</v>
       </c>
       <c r="E2">
-        <v>9041</v>
+        <v>9264</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -661,25 +565,25 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C3">
-        <v>1540</v>
+        <v>9396</v>
       </c>
       <c r="D3">
-        <v>77</v>
+        <v>469.8</v>
       </c>
       <c r="E3">
-        <v>1190</v>
+        <v>7054</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -687,262 +591,28 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>4017</v>
+        <v>20085</v>
       </c>
       <c r="D4">
-        <v>200.85</v>
+        <v>1004.25</v>
       </c>
       <c r="E4">
-        <v>2791</v>
+        <v>13401</v>
       </c>
       <c r="F4">
-        <v>23.4</v>
+        <v>117</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>375</v>
       </c>
       <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5">
-        <v>3328</v>
-      </c>
-      <c r="D5">
-        <v>166.4</v>
-      </c>
-      <c r="E5">
-        <v>2497</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6">
-        <v>5632</v>
-      </c>
-      <c r="D6">
-        <v>281.6</v>
-      </c>
-      <c r="E6">
-        <v>4274</v>
-      </c>
-      <c r="F6">
-        <v>20</v>
-      </c>
-      <c r="G6">
-        <v>50</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7">
-        <v>8034</v>
-      </c>
-      <c r="D7">
-        <v>401.7</v>
-      </c>
-      <c r="E7">
-        <v>5192</v>
-      </c>
-      <c r="F7">
-        <v>46.8</v>
-      </c>
-      <c r="G7">
-        <v>150</v>
-      </c>
-      <c r="H7">
-        <v>65.59999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>6656</v>
-      </c>
-      <c r="D8">
-        <v>332.8</v>
-      </c>
-      <c r="E8">
-        <v>4456</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>1994</v>
-      </c>
-      <c r="D9">
-        <v>99.7</v>
-      </c>
-      <c r="E9">
-        <v>1644</v>
-      </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>25</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10">
-        <v>5356</v>
-      </c>
-      <c r="D10">
-        <v>267.8</v>
-      </c>
-      <c r="E10">
-        <v>3857</v>
-      </c>
-      <c r="F10">
-        <v>31.2</v>
-      </c>
-      <c r="G10">
-        <v>100</v>
-      </c>
-      <c r="H10">
-        <v>65.59999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11">
-        <v>3328</v>
-      </c>
-      <c r="D11">
-        <v>166.4</v>
-      </c>
-      <c r="E11">
-        <v>2311</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12">
-        <v>3521</v>
-      </c>
-      <c r="D12">
-        <v>176.05</v>
-      </c>
-      <c r="E12">
-        <v>2066</v>
-      </c>
-      <c r="F12">
-        <v>30</v>
-      </c>
-      <c r="G12">
-        <v>75</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13">
-        <v>5356</v>
-      </c>
-      <c r="D13">
-        <v>267.8</v>
-      </c>
-      <c r="E13">
-        <v>3363</v>
-      </c>
-      <c r="F13">
-        <v>31.2</v>
-      </c>
-      <c r="G13">
-        <v>100</v>
-      </c>
-      <c r="H13">
-        <v>65.59999999999999</v>
+        <v>196.8</v>
       </c>
     </row>
   </sheetData>
@@ -952,92 +622,47 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
-      <c r="D2">
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
         <v>4</v>
       </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
         <v>27</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1047,57 +672,39 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
         <v>6</v>
       </c>
     </row>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,28 +43,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0308.csv</t>
-  </si>
-  <si>
-    <t>0309.csv</t>
-  </si>
-  <si>
-    <t>0310.csv</t>
-  </si>
-  <si>
-    <t>0311.csv</t>
+    <t>直邮店-0308.csv</t>
+  </si>
+  <si>
+    <t>直邮店-0315.csv</t>
   </si>
   <si>
     <t>2026-03-08</t>
   </si>
   <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
-    <t>2026-03-11</t>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>日期</t>
@@ -464,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -498,22 +486,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>17205</v>
+        <v>112718</v>
       </c>
       <c r="D2">
-        <v>860.25</v>
+        <v>5635.9</v>
       </c>
       <c r="E2">
-        <v>13022</v>
+        <v>79476</v>
       </c>
       <c r="F2">
-        <v>33.4</v>
+        <v>392.2</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>1250</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -524,77 +512,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>16994</v>
+        <v>42793</v>
       </c>
       <c r="D3">
-        <v>849.7</v>
+        <v>2139.65</v>
       </c>
       <c r="E3">
-        <v>11963</v>
+        <v>29719</v>
       </c>
       <c r="F3">
-        <v>66.8</v>
+        <v>157</v>
       </c>
       <c r="G3">
-        <v>200</v>
+        <v>475</v>
       </c>
       <c r="H3">
-        <v>65.59999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>14006</v>
-      </c>
-      <c r="D4">
-        <v>700.3</v>
-      </c>
-      <c r="E4">
-        <v>9957</v>
-      </c>
-      <c r="F4">
-        <v>41.2</v>
-      </c>
-      <c r="G4">
-        <v>125</v>
-      </c>
-      <c r="H4">
-        <v>65.59999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>12205</v>
-      </c>
-      <c r="D5">
-        <v>610.25</v>
-      </c>
-      <c r="E5">
-        <v>7740</v>
-      </c>
-      <c r="F5">
-        <v>61.2</v>
-      </c>
-      <c r="G5">
-        <v>175</v>
-      </c>
-      <c r="H5">
-        <v>65.59999999999999</v>
+        <v>196.8</v>
       </c>
     </row>
   </sheetData>
@@ -604,50 +540,50 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>11648</v>
+        <v>44578</v>
       </c>
       <c r="D2">
-        <v>582.4</v>
+        <v>2228.9</v>
       </c>
       <c r="E2">
-        <v>9041</v>
+        <v>31840</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -661,10 +597,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>1540</v>
@@ -687,25 +623,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>4017</v>
+        <v>66600</v>
       </c>
       <c r="D4">
-        <v>200.85</v>
+        <v>3330</v>
       </c>
       <c r="E4">
-        <v>2791</v>
+        <v>46446</v>
       </c>
       <c r="F4">
-        <v>23.4</v>
+        <v>382.2</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>1225</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -713,19 +649,19 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>3328</v>
+        <v>13312</v>
       </c>
       <c r="D5">
-        <v>166.4</v>
+        <v>665.6</v>
       </c>
       <c r="E5">
-        <v>2497</v>
+        <v>9264</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -739,25 +675,25 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>5632</v>
+        <v>9396</v>
       </c>
       <c r="D6">
-        <v>281.6</v>
+        <v>469.8</v>
       </c>
       <c r="E6">
-        <v>4274</v>
+        <v>7054</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -765,184 +701,28 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C7">
-        <v>8034</v>
+        <v>20085</v>
       </c>
       <c r="D7">
-        <v>401.7</v>
+        <v>1004.25</v>
       </c>
       <c r="E7">
-        <v>5192</v>
+        <v>13401</v>
       </c>
       <c r="F7">
-        <v>46.8</v>
+        <v>117</v>
       </c>
       <c r="G7">
-        <v>150</v>
+        <v>375</v>
       </c>
       <c r="H7">
-        <v>65.59999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>6656</v>
-      </c>
-      <c r="D8">
-        <v>332.8</v>
-      </c>
-      <c r="E8">
-        <v>4456</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>1994</v>
-      </c>
-      <c r="D9">
-        <v>99.7</v>
-      </c>
-      <c r="E9">
-        <v>1644</v>
-      </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>25</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10">
-        <v>5356</v>
-      </c>
-      <c r="D10">
-        <v>267.8</v>
-      </c>
-      <c r="E10">
-        <v>3857</v>
-      </c>
-      <c r="F10">
-        <v>31.2</v>
-      </c>
-      <c r="G10">
-        <v>100</v>
-      </c>
-      <c r="H10">
-        <v>65.59999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11">
-        <v>3328</v>
-      </c>
-      <c r="D11">
-        <v>166.4</v>
-      </c>
-      <c r="E11">
-        <v>2311</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12">
-        <v>3521</v>
-      </c>
-      <c r="D12">
-        <v>176.05</v>
-      </c>
-      <c r="E12">
-        <v>2066</v>
-      </c>
-      <c r="F12">
-        <v>30</v>
-      </c>
-      <c r="G12">
-        <v>75</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13">
-        <v>5356</v>
-      </c>
-      <c r="D13">
-        <v>267.8</v>
-      </c>
-      <c r="E13">
-        <v>3363</v>
-      </c>
-      <c r="F13">
-        <v>31.2</v>
-      </c>
-      <c r="G13">
-        <v>100</v>
-      </c>
-      <c r="H13">
-        <v>65.59999999999999</v>
+        <v>196.8</v>
       </c>
     </row>
   </sheetData>
@@ -952,92 +732,62 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
+        <v>49</v>
+      </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="C5">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1047,57 +797,39 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
         <v>6</v>
       </c>
     </row>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
   <si>
     <t>文件名称</t>
   </si>
@@ -79,16 +79,22 @@
     <t>其他</t>
   </si>
   <si>
-    <t>头发护理精华</t>
-  </si>
-  <si>
     <t>电动鼻毛刀</t>
   </si>
   <si>
+    <t>镁膏</t>
+  </si>
+  <si>
     <t>商品名称</t>
   </si>
   <si>
     <t>剪影贴纸</t>
+  </si>
+  <si>
+    <t>新款睫毛夹</t>
+  </si>
+  <si>
+    <t>草莓捏捏乐</t>
   </si>
   <si>
     <t>汇总</t>
@@ -498,10 +504,10 @@
         <v>79476</v>
       </c>
       <c r="F2">
-        <v>392.2</v>
+        <v>382.2</v>
       </c>
       <c r="G2">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -524,10 +530,10 @@
         <v>29719</v>
       </c>
       <c r="F3">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G3">
-        <v>475</v>
+        <v>441</v>
       </c>
       <c r="H3">
         <v>196.8</v>
@@ -540,7 +546,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -577,13 +583,13 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>44578</v>
+        <v>46118</v>
       </c>
       <c r="D2">
-        <v>2228.9</v>
+        <v>2305.9</v>
       </c>
       <c r="E2">
-        <v>31840</v>
+        <v>33030</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -603,19 +609,19 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>1540</v>
+        <v>66600</v>
       </c>
       <c r="D3">
-        <v>77</v>
+        <v>3330</v>
       </c>
       <c r="E3">
-        <v>1190</v>
+        <v>46446</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>382.2</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>1225</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -623,25 +629,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>66600</v>
+        <v>15082</v>
       </c>
       <c r="D4">
-        <v>3330</v>
+        <v>754.1</v>
       </c>
       <c r="E4">
-        <v>46446</v>
+        <v>10400</v>
       </c>
       <c r="F4">
-        <v>382.2</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1225</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -652,25 +658,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5">
-        <v>13312</v>
+        <v>20085</v>
       </c>
       <c r="D5">
-        <v>665.6</v>
+        <v>1004.25</v>
       </c>
       <c r="E5">
-        <v>9264</v>
+        <v>13401</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>196.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -678,51 +684,25 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6">
-        <v>9396</v>
+        <v>7626</v>
       </c>
       <c r="D6">
-        <v>469.8</v>
+        <v>381.3</v>
       </c>
       <c r="E6">
-        <v>7054</v>
+        <v>5918</v>
       </c>
       <c r="F6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="H6">
         <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7">
-        <v>20085</v>
-      </c>
-      <c r="D7">
-        <v>1004.25</v>
-      </c>
-      <c r="E7">
-        <v>13401</v>
-      </c>
-      <c r="F7">
-        <v>117</v>
-      </c>
-      <c r="G7">
-        <v>375</v>
-      </c>
-      <c r="H7">
-        <v>196.8</v>
       </c>
     </row>
   </sheetData>
@@ -732,7 +712,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -748,7 +728,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>49</v>
@@ -770,23 +750,45 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7">
         <v>76</v>
       </c>
-      <c r="C5">
+      <c r="C7">
         <v>27</v>
       </c>
     </row>
@@ -808,12 +810,12 @@
         <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -824,7 +826,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>6</v>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>直邮店-0308.csv</t>
-  </si>
-  <si>
-    <t>直邮店-0315.csv</t>
-  </si>
-  <si>
-    <t>2026-03-08</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
+    <t>0322week.csv</t>
+  </si>
+  <si>
+    <t>0329week.csv</t>
+  </si>
+  <si>
+    <t>2026-03-22</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
   </si>
   <si>
     <t>日期</t>
@@ -76,25 +76,19 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>其他</t>
+    <t>头发护理精华</t>
+  </si>
+  <si>
+    <t>电动剃眉刀</t>
   </si>
   <si>
     <t>电动鼻毛刀</t>
   </si>
   <si>
-    <t>镁膏</t>
-  </si>
-  <si>
-    <t>商品名称</t>
-  </si>
-  <si>
-    <t>剪影贴纸</t>
-  </si>
-  <si>
-    <t>新款睫毛夹</t>
-  </si>
-  <si>
-    <t>草莓捏捏乐</t>
+    <t>车载手机支架</t>
+  </si>
+  <si>
+    <t>产品名称</t>
   </si>
   <si>
     <t>汇总</t>
@@ -495,22 +489,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>112718</v>
+        <v>140377</v>
       </c>
       <c r="D2">
-        <v>5635.9</v>
+        <v>7018.85</v>
       </c>
       <c r="E2">
-        <v>79476</v>
+        <v>128505</v>
       </c>
       <c r="F2">
-        <v>382.2</v>
+        <v>1142.2</v>
       </c>
       <c r="G2">
-        <v>1225</v>
+        <v>3595</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>648.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -521,22 +515,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>42793</v>
+        <v>197774</v>
       </c>
       <c r="D3">
-        <v>2139.65</v>
+        <v>9888.700000000001</v>
       </c>
       <c r="E3">
-        <v>29719</v>
+        <v>188256</v>
       </c>
       <c r="F3">
-        <v>153</v>
+        <v>1838.4</v>
       </c>
       <c r="G3">
-        <v>441</v>
+        <v>5840</v>
       </c>
       <c r="H3">
-        <v>196.8</v>
+        <v>647.3</v>
       </c>
     </row>
   </sheetData>
@@ -546,7 +540,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -583,19 +577,19 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>46118</v>
+        <v>5488</v>
       </c>
       <c r="D2">
-        <v>2305.9</v>
+        <v>274.4</v>
       </c>
       <c r="E2">
-        <v>33030</v>
+        <v>5135</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -609,74 +603,74 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>66600</v>
+        <v>26256</v>
       </c>
       <c r="D3">
-        <v>3330</v>
+        <v>1312.8</v>
       </c>
       <c r="E3">
-        <v>46446</v>
+        <v>21830</v>
       </c>
       <c r="F3">
-        <v>382.2</v>
+        <v>128.8</v>
       </c>
       <c r="G3">
-        <v>1225</v>
+        <v>350</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>222.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>15082</v>
+        <v>104313</v>
       </c>
       <c r="D4">
-        <v>754.1</v>
+        <v>5215.65</v>
       </c>
       <c r="E4">
-        <v>10400</v>
+        <v>97220</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3125</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>426.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>20085</v>
+        <v>4320</v>
       </c>
       <c r="D5">
-        <v>1004.25</v>
+        <v>216</v>
       </c>
       <c r="E5">
-        <v>13401</v>
+        <v>4320</v>
       </c>
       <c r="F5">
-        <v>117</v>
+        <v>18.4</v>
       </c>
       <c r="G5">
-        <v>375</v>
+        <v>70</v>
       </c>
       <c r="H5">
-        <v>196.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -684,24 +678,102 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>1960</v>
+      </c>
+      <c r="D6">
+        <v>98</v>
+      </c>
+      <c r="E6">
+        <v>1960</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>24316</v>
+      </c>
+      <c r="D7">
+        <v>1215.8</v>
+      </c>
+      <c r="E7">
+        <v>21289</v>
+      </c>
+      <c r="F7">
+        <v>138</v>
+      </c>
+      <c r="G7">
+        <v>375</v>
+      </c>
+      <c r="H7">
+        <v>188.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="C6">
-        <v>7626</v>
-      </c>
-      <c r="D6">
-        <v>381.3</v>
-      </c>
-      <c r="E6">
-        <v>5918</v>
-      </c>
-      <c r="F6">
-        <v>36</v>
-      </c>
-      <c r="G6">
-        <v>66</v>
-      </c>
-      <c r="H6">
+      <c r="C8">
+        <v>165994</v>
+      </c>
+      <c r="D8">
+        <v>8299.700000000001</v>
+      </c>
+      <c r="E8">
+        <v>159543</v>
+      </c>
+      <c r="F8">
+        <v>1653.6</v>
+      </c>
+      <c r="G8">
+        <v>5300</v>
+      </c>
+      <c r="H8">
+        <v>459.1999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>5504</v>
+      </c>
+      <c r="D9">
+        <v>275.2</v>
+      </c>
+      <c r="E9">
+        <v>5464</v>
+      </c>
+      <c r="F9">
+        <v>36.8</v>
+      </c>
+      <c r="G9">
+        <v>140</v>
+      </c>
+      <c r="H9">
         <v>0</v>
       </c>
     </row>
@@ -712,12 +784,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -728,68 +800,57 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
-        <v>76</v>
-      </c>
-      <c r="C7">
-        <v>27</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -799,40 +860,63 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="B3">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4">
         <v>26</v>
       </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>6</v>
+      <c r="C4">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,18 +43,18 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0322week.csv</t>
-  </si>
-  <si>
     <t>0329week.csv</t>
   </si>
   <si>
-    <t>2026-03-22</t>
+    <t>0405week.csv</t>
   </si>
   <si>
     <t>2026-03-29</t>
   </si>
   <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -77,15 +77,6 @@
   </si>
   <si>
     <t>头发护理精华</t>
-  </si>
-  <si>
-    <t>电动剃眉刀</t>
-  </si>
-  <si>
-    <t>电动鼻毛刀</t>
-  </si>
-  <si>
-    <t>车载手机支架</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -489,22 +480,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>140377</v>
+        <v>13776</v>
       </c>
       <c r="D2">
-        <v>7018.85</v>
+        <v>688.8</v>
       </c>
       <c r="E2">
-        <v>128505</v>
+        <v>11151</v>
       </c>
       <c r="F2">
-        <v>1142.2</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>3595</v>
+        <v>150</v>
       </c>
       <c r="H2">
-        <v>648.7</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -515,22 +506,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>197774</v>
+        <v>3520</v>
       </c>
       <c r="D3">
-        <v>9888.700000000001</v>
+        <v>176</v>
       </c>
       <c r="E3">
-        <v>188256</v>
+        <v>2843</v>
       </c>
       <c r="F3">
-        <v>1838.4</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>5840</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>647.3</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -540,7 +531,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -577,204 +568,48 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>5488</v>
+        <v>13776</v>
       </c>
       <c r="D2">
-        <v>274.4</v>
+        <v>688.8</v>
       </c>
       <c r="E2">
-        <v>5135</v>
+        <v>11151</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>3520</v>
+      </c>
+      <c r="D3">
+        <v>176</v>
+      </c>
+      <c r="E3">
+        <v>2843</v>
+      </c>
+      <c r="F3">
         <v>20</v>
       </c>
-      <c r="C3">
-        <v>26256</v>
-      </c>
-      <c r="D3">
-        <v>1312.8</v>
-      </c>
-      <c r="E3">
-        <v>21830</v>
-      </c>
-      <c r="F3">
-        <v>128.8</v>
-      </c>
       <c r="G3">
-        <v>350</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>222.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4">
-        <v>104313</v>
-      </c>
-      <c r="D4">
-        <v>5215.65</v>
-      </c>
-      <c r="E4">
-        <v>97220</v>
-      </c>
-      <c r="F4">
-        <v>975</v>
-      </c>
-      <c r="G4">
-        <v>3125</v>
-      </c>
-      <c r="H4">
-        <v>426.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5">
-        <v>4320</v>
-      </c>
-      <c r="D5">
-        <v>216</v>
-      </c>
-      <c r="E5">
-        <v>4320</v>
-      </c>
-      <c r="F5">
-        <v>18.4</v>
-      </c>
-      <c r="G5">
-        <v>70</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6">
-        <v>1960</v>
-      </c>
-      <c r="D6">
-        <v>98</v>
-      </c>
-      <c r="E6">
-        <v>1960</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>25</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>24316</v>
-      </c>
-      <c r="D7">
-        <v>1215.8</v>
-      </c>
-      <c r="E7">
-        <v>21289</v>
-      </c>
-      <c r="F7">
-        <v>138</v>
-      </c>
-      <c r="G7">
-        <v>375</v>
-      </c>
-      <c r="H7">
-        <v>188.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8">
-        <v>165994</v>
-      </c>
-      <c r="D8">
-        <v>8299.700000000001</v>
-      </c>
-      <c r="E8">
-        <v>159543</v>
-      </c>
-      <c r="F8">
-        <v>1653.6</v>
-      </c>
-      <c r="G8">
-        <v>5300</v>
-      </c>
-      <c r="H8">
-        <v>459.1999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9">
-        <v>5504</v>
-      </c>
-      <c r="D9">
-        <v>275.2</v>
-      </c>
-      <c r="E9">
-        <v>5464</v>
-      </c>
-      <c r="F9">
-        <v>36.8</v>
-      </c>
-      <c r="G9">
-        <v>140</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -784,12 +619,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -800,57 +635,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>212</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
         <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6">
-        <v>159</v>
-      </c>
-      <c r="C6">
-        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -860,12 +662,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -874,49 +676,35 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>13</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>13</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
-        <v>26</v>
-      </c>
-      <c r="C4">
-        <v>25</v>
-      </c>
-      <c r="D4">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,10 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0329week.csv</t>
-  </si>
-  <si>
-    <t>0405week.csv</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
+    <t>0301-0331.csv</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>日期</t>
@@ -76,7 +70,19 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>头发护理精华</t>
+    <t>剪影贴纸</t>
+  </si>
+  <si>
+    <t>新款睫毛夹</t>
+  </si>
+  <si>
+    <t>电动鼻毛刀</t>
+  </si>
+  <si>
+    <t>草莓捏捏乐</t>
+  </si>
+  <si>
+    <t>镁膏</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -443,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -477,51 +483,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>13776</v>
+        <v>148855</v>
       </c>
       <c r="D2">
-        <v>688.8</v>
+        <v>7442.75</v>
       </c>
       <c r="E2">
-        <v>11151</v>
+        <v>104662</v>
       </c>
       <c r="F2">
-        <v>60</v>
+        <v>535.2</v>
       </c>
       <c r="G2">
-        <v>150</v>
+        <v>1666</v>
       </c>
       <c r="H2">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>3520</v>
-      </c>
-      <c r="D3">
-        <v>176</v>
-      </c>
-      <c r="E3">
-        <v>2843</v>
-      </c>
-      <c r="F3">
-        <v>20</v>
-      </c>
-      <c r="G3">
-        <v>50</v>
-      </c>
-      <c r="H3">
-        <v>595</v>
+        <v>131.2</v>
       </c>
     </row>
   </sheetData>
@@ -531,85 +511,163 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C2">
-        <v>13776</v>
+        <v>51234</v>
       </c>
       <c r="D2">
-        <v>688.8</v>
+        <v>2561.7</v>
       </c>
       <c r="E2">
-        <v>11151</v>
+        <v>36571</v>
       </c>
       <c r="F2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>1540</v>
+      </c>
+      <c r="D3">
+        <v>77</v>
+      </c>
+      <c r="E3">
+        <v>1190</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C3">
-        <v>3520</v>
-      </c>
-      <c r="D3">
-        <v>176</v>
-      </c>
-      <c r="E3">
-        <v>2843</v>
-      </c>
-      <c r="F3">
+      <c r="C4">
+        <v>86685</v>
+      </c>
+      <c r="D4">
+        <v>4334.25</v>
+      </c>
+      <c r="E4">
+        <v>59847</v>
+      </c>
+      <c r="F4">
+        <v>499.2</v>
+      </c>
+      <c r="G4">
+        <v>1600</v>
+      </c>
+      <c r="H4">
+        <v>131.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="G3">
-        <v>50</v>
-      </c>
-      <c r="H3">
-        <v>595</v>
+      <c r="C5">
+        <v>1770</v>
+      </c>
+      <c r="D5">
+        <v>88.5</v>
+      </c>
+      <c r="E5">
+        <v>1136</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6">
+        <v>7626</v>
+      </c>
+      <c r="D6">
+        <v>381.3</v>
+      </c>
+      <c r="E6">
+        <v>5918</v>
+      </c>
+      <c r="F6">
+        <v>36</v>
+      </c>
+      <c r="G6">
+        <v>66</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -619,40 +677,63 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -662,49 +743,40 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>17</v>
-      </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>17</v>
-      </c>
-      <c r="D3">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="32">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,12 +43,24 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0301-0331.csv</t>
+    <t>日本直邮店-2月份.csv</t>
+  </si>
+  <si>
+    <t>日本直邮店-3月份.csv</t>
+  </si>
+  <si>
+    <t>日本直邮店-4月份.csv</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
   </si>
   <si>
     <t>2026-03-12</t>
   </si>
   <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -70,13 +82,22 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>头发护理精华</t>
+  </si>
+  <si>
+    <t>新款睫毛夹</t>
+  </si>
+  <si>
+    <t>椰子捏捏乐</t>
+  </si>
+  <si>
+    <t>电动鼻毛刀</t>
+  </si>
+  <si>
+    <t>蓝牙MP3</t>
+  </si>
+  <si>
     <t>剪影贴纸</t>
-  </si>
-  <si>
-    <t>新款睫毛夹</t>
-  </si>
-  <si>
-    <t>电动鼻毛刀</t>
   </si>
   <si>
     <t>草莓捏捏乐</t>
@@ -98,16 +119,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -123,7 +136,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -131,30 +144,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,32 +444,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -483,25 +478,77 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>348470</v>
+      </c>
+      <c r="D2">
+        <v>17423.5</v>
+      </c>
+      <c r="E2">
+        <v>241982</v>
+      </c>
+      <c r="F2">
+        <v>2020.8</v>
+      </c>
+      <c r="G2">
+        <v>6349.02</v>
+      </c>
+      <c r="H2">
+        <v>1935.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
         <v>148855</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>7442.75</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>104662</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>535.2</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>1666</v>
       </c>
-      <c r="H2">
+      <c r="H3">
         <v>131.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>16025</v>
+      </c>
+      <c r="D4">
+        <v>801.25</v>
+      </c>
+      <c r="E4">
+        <v>11734</v>
+      </c>
+      <c r="F4">
+        <v>70.2</v>
+      </c>
+      <c r="G4">
+        <v>225</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -511,56 +558,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>16</v>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C2">
-        <v>51234</v>
+        <v>4499</v>
       </c>
       <c r="D2">
-        <v>2561.7</v>
+        <v>224.95</v>
       </c>
       <c r="E2">
-        <v>36571</v>
+        <v>3309</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -568,10 +615,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>1540</v>
@@ -594,79 +641,261 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4">
-        <v>86685</v>
+        <v>1661</v>
       </c>
       <c r="D4">
-        <v>4334.25</v>
+        <v>83.05</v>
       </c>
       <c r="E4">
-        <v>59847</v>
+        <v>1114</v>
       </c>
       <c r="F4">
-        <v>499.2</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>131.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5">
-        <v>1770</v>
+        <v>338729</v>
       </c>
       <c r="D5">
-        <v>88.5</v>
+        <v>16936.45</v>
       </c>
       <c r="E5">
-        <v>1136</v>
+        <v>235101</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1957.8</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>6275</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1935.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C6">
+        <v>2041</v>
+      </c>
+      <c r="D6">
+        <v>102.05</v>
+      </c>
+      <c r="E6">
+        <v>1268</v>
+      </c>
+      <c r="F6">
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <v>24.02</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>51234</v>
+      </c>
+      <c r="D7">
+        <v>2561.7</v>
+      </c>
+      <c r="E7">
+        <v>36571</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>1540</v>
+      </c>
+      <c r="D8">
+        <v>77</v>
+      </c>
+      <c r="E8">
+        <v>1190</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>86685</v>
+      </c>
+      <c r="D9">
+        <v>4334.25</v>
+      </c>
+      <c r="E9">
+        <v>59847</v>
+      </c>
+      <c r="F9">
+        <v>499.2</v>
+      </c>
+      <c r="G9">
+        <v>1600</v>
+      </c>
+      <c r="H9">
+        <v>131.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10">
+        <v>1770</v>
+      </c>
+      <c r="D10">
+        <v>88.5</v>
+      </c>
+      <c r="E10">
+        <v>1136</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11">
         <v>7626</v>
       </c>
-      <c r="D6">
+      <c r="D11">
         <v>381.3</v>
       </c>
-      <c r="E6">
+      <c r="E11">
         <v>5918</v>
       </c>
-      <c r="F6">
+      <c r="F11">
         <v>36</v>
       </c>
-      <c r="G6">
+      <c r="G11">
         <v>66</v>
       </c>
-      <c r="H6">
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12">
+        <v>1664</v>
+      </c>
+      <c r="D12">
+        <v>83.2</v>
+      </c>
+      <c r="E12">
+        <v>1183</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13">
+        <v>14361</v>
+      </c>
+      <c r="D13">
+        <v>718.05</v>
+      </c>
+      <c r="E13">
+        <v>10551</v>
+      </c>
+      <c r="F13">
+        <v>70.2</v>
+      </c>
+      <c r="G13">
+        <v>225</v>
+      </c>
+      <c r="H13">
         <v>0</v>
       </c>
     </row>
@@ -677,63 +906,147 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2">
+        <v>251</v>
+      </c>
+      <c r="C2">
+        <v>64</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>22</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>23</v>
       </c>
-      <c r="B7">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10">
+        <v>256</v>
+      </c>
+      <c r="C10">
         <v>99</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -743,40 +1056,63 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="B2">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>23</v>
+      <c r="D2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>22</v>
       </c>
       <c r="B3">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4">
+        <v>70</v>
+      </c>
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>4</v>
+      <c r="D4">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_direct.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,22 +43,10 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>日本直邮店-2月份.csv</t>
-  </si>
-  <si>
-    <t>日本直邮店-3月份.csv</t>
-  </si>
-  <si>
-    <t>日本直邮店-4月份.csv</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
+    <t>日本直邮店-5月份.csv</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
   </si>
   <si>
     <t>日期</t>
@@ -82,28 +70,25 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>头发护理精华</t>
-  </si>
-  <si>
-    <t>新款睫毛夹</t>
-  </si>
-  <si>
-    <t>椰子捏捏乐</t>
+    <t>3.5号 夜光エギ 19g 13.5cm ラトル入り 重り付き シャクリ用 イカ釣り 疑似餌</t>
+  </si>
+  <si>
+    <t>【2WAY・多用途】シャンプーブラシ シリコン 頭皮マッサージ＆ペット用ブラシ 泡立ち抜群 詰め替え可能 男女兼用 犬・猫・うさぎ バス用品 お風呂グッズ （シリコン製・滑り止めグリップ）</t>
+  </si>
+  <si>
+    <t>【驚異の爆釣】3.5号 エギ 3段フック 夜光 蓄光 イカ釣り 仕掛け ルアー 餌木 アオリイカ 堤防 海釣り 疑似餌</t>
+  </si>
+  <si>
+    <t>ペット用 抜け毛取りブラシ 痛くない 毛玉ケア 涼しく過ごせるよう毛皮を薄く 犬猫用抜け毛取りコーム ステンレス製 人間工学グリップ 小型犬 中型犬 猫 トリミング グルーミング 換毛 お手入れ用品 熱中症対策 ペットブラシ(ピンク)</t>
   </si>
   <si>
     <t>电动鼻毛刀</t>
   </si>
   <si>
-    <t>蓝牙MP3</t>
-  </si>
-  <si>
-    <t>剪影贴纸</t>
-  </si>
-  <si>
-    <t>草莓捏捏乐</t>
-  </si>
-  <si>
-    <t>镁膏</t>
+    <t>自动折叠雨伞</t>
+  </si>
+  <si>
+    <t>超音波式蚊取り器 化学成分不使用 360° 音波ガード LEDライト付き赤ちゃんにも安心</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -444,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -478,77 +463,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>348470</v>
+        <v>39831</v>
       </c>
       <c r="D2">
-        <v>17423.5</v>
+        <v>1991.55</v>
       </c>
       <c r="E2">
-        <v>241982</v>
+        <v>24477</v>
       </c>
       <c r="F2">
-        <v>2020.8</v>
+        <v>260.6</v>
       </c>
       <c r="G2">
-        <v>6349.02</v>
+        <v>800</v>
       </c>
       <c r="H2">
-        <v>1935.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3">
-        <v>148855</v>
-      </c>
-      <c r="D3">
-        <v>7442.75</v>
-      </c>
-      <c r="E3">
-        <v>104662</v>
-      </c>
-      <c r="F3">
-        <v>535.2</v>
-      </c>
-      <c r="G3">
-        <v>1666</v>
-      </c>
-      <c r="H3">
-        <v>131.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>16025</v>
-      </c>
-      <c r="D4">
-        <v>801.25</v>
-      </c>
-      <c r="E4">
-        <v>11734</v>
-      </c>
-      <c r="F4">
-        <v>70.2</v>
-      </c>
-      <c r="G4">
-        <v>225</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
+        <v>951.2</v>
       </c>
     </row>
   </sheetData>
@@ -558,56 +491,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C2">
-        <v>4499</v>
+        <v>7301</v>
       </c>
       <c r="D2">
-        <v>224.95</v>
+        <v>365.05</v>
       </c>
       <c r="E2">
-        <v>3309</v>
+        <v>5489</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -615,19 +548,19 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C3">
-        <v>1540</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1190</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -641,19 +574,19 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>1661</v>
+        <v>1025</v>
       </c>
       <c r="D4">
-        <v>83.05</v>
+        <v>51.25</v>
       </c>
       <c r="E4">
-        <v>1114</v>
+        <v>675</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -667,74 +600,74 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5">
-        <v>338729</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>16936.45</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>235101</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>1957.8</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>6275</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1935.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6">
-        <v>2041</v>
+        <v>27676</v>
       </c>
       <c r="D6">
-        <v>102.05</v>
+        <v>1383.8</v>
       </c>
       <c r="E6">
-        <v>1268</v>
+        <v>15593</v>
       </c>
       <c r="F6">
-        <v>43</v>
+        <v>249.6</v>
       </c>
       <c r="G6">
-        <v>24.02</v>
+        <v>800</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>951.1999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>51234</v>
+        <v>1949</v>
       </c>
       <c r="D7">
-        <v>2561.7</v>
+        <v>97.45</v>
       </c>
       <c r="E7">
-        <v>36571</v>
+        <v>1599</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -745,19 +678,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>1540</v>
+        <v>1880</v>
       </c>
       <c r="D8">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E8">
-        <v>1190</v>
+        <v>1121</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -766,136 +699,6 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>86685</v>
-      </c>
-      <c r="D9">
-        <v>4334.25</v>
-      </c>
-      <c r="E9">
-        <v>59847</v>
-      </c>
-      <c r="F9">
-        <v>499.2</v>
-      </c>
-      <c r="G9">
-        <v>1600</v>
-      </c>
-      <c r="H9">
-        <v>131.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10">
-        <v>1770</v>
-      </c>
-      <c r="D10">
-        <v>88.5</v>
-      </c>
-      <c r="E10">
-        <v>1136</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11">
-        <v>7626</v>
-      </c>
-      <c r="D11">
-        <v>381.3</v>
-      </c>
-      <c r="E11">
-        <v>5918</v>
-      </c>
-      <c r="F11">
-        <v>36</v>
-      </c>
-      <c r="G11">
-        <v>66</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12">
-        <v>1664</v>
-      </c>
-      <c r="D12">
-        <v>83.2</v>
-      </c>
-      <c r="E12">
-        <v>1183</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13">
-        <v>14361</v>
-      </c>
-      <c r="D13">
-        <v>718.05</v>
-      </c>
-      <c r="E13">
-        <v>10551</v>
-      </c>
-      <c r="F13">
-        <v>70.2</v>
-      </c>
-      <c r="G13">
-        <v>225</v>
-      </c>
-      <c r="H13">
         <v>0</v>
       </c>
     </row>
@@ -906,147 +709,63 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>251</v>
-      </c>
-      <c r="C2">
-        <v>64</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>30</v>
-      </c>
-      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10">
-        <v>256</v>
-      </c>
-      <c r="C10">
-        <v>99</v>
-      </c>
-      <c r="D10">
-        <v>10</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1056,63 +775,73 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
         <v>29</v>
       </c>
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2">
-        <v>59</v>
-      </c>
       <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>27</v>
+      </c>
+      <c r="C3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
         <v>22</v>
       </c>
-      <c r="B3">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4">
-        <v>70</v>
-      </c>
       <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>74</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>84</v>
+      </c>
+      <c r="C6">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
